--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R818fd2b95add4f1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="2" r:id="Ree2260e949d049b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" r:id="Rf6a39b1ad36c4fba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updates" sheetId="4" r:id="Rc3825060b1204ec5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="5" r:id="R6676fbec0a274fb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Website Export" sheetId="6" r:id="R19e4e37c7e4d4f63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Re19d673467a445ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="2" r:id="R5440c47544f5463d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" r:id="Rafeb7296dc2d47ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updates" sheetId="4" r:id="Rfd4434d03244424c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="5" r:id="R708fda16524c41f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Website Export" sheetId="6" r:id="Ra5ffc5103f1748a8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -824,11 +824,11 @@
       <x:c r="F2">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G2">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="H2">
-        <x:v>270</x:v>
+      <x:c r="G2" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H2" t="n">
+        <x:v>404</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1290,11 +1290,11 @@
       </x:c>
       <x:c r="O2" s="6" t="n">
         <x:f>IF(B2="","",IF(K2="INVALID — CHECK RESULT TYPE","",VLOOKUP(B2,Baseline!$A$2:$H$10,7,FALSE)+IF(K2="Transfer",1,0)))</x:f>
-        <x:v>172</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="P2" s="6" t="n">
         <x:f>IF(B2="","",IF(K2="INVALID — CHECK RESULT TYPE","",VLOOKUP(B2,Baseline!$A$2:$H$10,8,FALSE)+IF(K2="Defence",1,0)))</x:f>
-        <x:v>270</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="Q2" s="5"/>
       <x:c r="R2" s="32" t="n">
@@ -5025,11 +5025,11 @@
       </x:c>
       <x:c r="E2" t="n">
         <x:f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$O$2:$O$100),VLOOKUP(A2,Baseline!$A$2:$H$10,7,FALSE))</x:f>
-        <x:v>172</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="F2" t="n">
         <x:f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$P$2:$P$100),VLOOKUP(A2,Baseline!$A$2:$H$10,8,FALSE))</x:f>
-        <x:v>270</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="G2" s="4" t="n">
         <x:f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A2)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</x:f>
@@ -5362,11 +5362,11 @@
       </x:c>
       <x:c r="E2" t="n">
         <x:f>Dashboard!E2</x:f>
-        <x:v>172</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="F2" t="n">
         <x:f>Dashboard!F2</x:f>
-        <x:v>270</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="G2" s="9" t="n">
         <x:f>Dashboard!G2</x:f>

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\lineal website\Live Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A115BB4-2237-479F-935E-71B8537758C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9F000B-7CD2-4495-B949-87A23E55759E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="START HERE" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="118">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -387,6 +387,9 @@
   </si>
   <si>
     <t>def Zimbabwe by 59 runs</t>
+  </si>
+  <si>
+    <t>def Zimbabwe by 84 runs</t>
   </si>
 </sst>
 </file>
@@ -1732,10 +1735,14 @@
         <v>90</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="10"/>
+        <v>63</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>117</v>
+      </c>
       <c r="I10" s="5"/>
       <c r="J10" s="6" t="str">
         <f>IF(B10="","",IFERROR(LOOKUP(2,1/($B$2:B9=B10),$L$2:L9),VLOOKUP(B10,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1743,7 +1750,7 @@
       </c>
       <c r="K10" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Scheduled</v>
+        <v>Defence</v>
       </c>
       <c r="L10" s="6" t="str">
         <f t="shared" si="1"/>
@@ -1755,7 +1762,7 @@
       </c>
       <c r="N10" s="6">
         <f>IF(B10="","",IF(K10="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B9=B10),$N$2:N9),VLOOKUP(B10,Baseline!$A$2:$H$10,6,FALSE))+IF(K10="Defence",1,0)))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" s="6">
         <f>IF(B10="","",IFERROR(LOOKUP(2,1/($B$2:B9=B10),$O$2:O9),VLOOKUP(B10,Baseline!$A$2:$H$10,7,FALSE))+IF(K10="Transfer",1,0))</f>
@@ -1763,7 +1770,7 @@
       </c>
       <c r="P10" s="6">
         <f>IF(B10="","",IFERROR(LOOKUP(2,1/($B$2:B9=B10),$P$2:P9),VLOOKUP(B10,Baseline!$A$2:$H$10,8,FALSE))+IF(K10="Defence",1,0))</f>
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="Q10" s="5"/>
       <c r="R10" s="12"/>
@@ -1771,43 +1778,53 @@
     <row r="11" spans="1:18">
       <c r="A11" s="6" t="str">
         <f>IF(OR(B11="",C11=""),"",VLOOKUP(B11,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C11,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B11,B11,$C$2:C11,C11),"00"))</f>
-        <v/>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+        <v>JEJ-20260920-01</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="7">
+        <v>46285</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="G11" s="5"/>
       <c r="H11" s="10"/>
       <c r="I11" s="5"/>
       <c r="J11" s="6" t="str">
         <f>IF(B11="","",IFERROR(LOOKUP(2,1/($B$2:B10=B11),$L$2:L10),VLOOKUP(B11,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v/>
+        <v>Australia</v>
       </c>
       <c r="K11" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="L11" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M11" s="8" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="M11" s="8">
         <f>IF(B11="","",IF(K11="Transfer",C11,IFERROR(LOOKUP(2,1/($B$2:B10=B11),$M$2:M10),VLOOKUP(B11,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v/>
-      </c>
-      <c r="N11" s="6" t="str">
+        <v>46187</v>
+      </c>
+      <c r="N11" s="6">
         <f>IF(B11="","",IF(K11="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B10=B11),$N$2:N10),VLOOKUP(B11,Baseline!$A$2:$H$10,6,FALSE))+IF(K11="Defence",1,0)))</f>
-        <v/>
-      </c>
-      <c r="O11" s="6" t="str">
+        <v>2</v>
+      </c>
+      <c r="O11" s="6">
         <f>IF(B11="","",IFERROR(LOOKUP(2,1/($B$2:B10=B11),$O$2:O10),VLOOKUP(B11,Baseline!$A$2:$H$10,7,FALSE))+IF(K11="Transfer",1,0))</f>
-        <v/>
-      </c>
-      <c r="P11" s="6" t="str">
+        <v>358</v>
+      </c>
+      <c r="P11" s="6">
         <f>IF(B11="","",IFERROR(LOOKUP(2,1/($B$2:B10=B11),$P$2:P10),VLOOKUP(B11,Baseline!$A$2:$H$10,8,FALSE))+IF(K11="Defence",1,0))</f>
-        <v/>
+        <v>598</v>
       </c>
       <c r="Q11" s="5"/>
       <c r="R11" s="12"/>
@@ -5871,7 +5888,7 @@
       </c>
       <c r="D4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$N$2:$N$100),VLOOKUP(A4,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$O$2:$O$100),VLOOKUP(A4,Baseline!$A$2:$H$10,7,FALSE))</f>
@@ -5879,11 +5896,11 @@
       </c>
       <c r="F4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$P$2:$P$100),VLOOKUP(A4,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G4" s="4">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A4)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="H4" t="str">
         <f>IF(G4="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A4)*(Updates!$C$2:$C$100=G4)),Updates!$D$2:$D$100),"TBD"))</f>
@@ -6211,7 +6228,7 @@
       </c>
       <c r="D4">
         <f>Dashboard!D4</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <f>Dashboard!E4</f>
@@ -6219,11 +6236,11 @@
       </c>
       <c r="F4">
         <f>Dashboard!F4</f>
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G4" s="9">
         <f>Dashboard!G4</f>
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="H4" t="str">
         <f>Dashboard!H4</f>

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\lineal website\Live Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9F000B-7CD2-4495-B949-87A23E55759E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA03D3B-9C2B-411F-BD3B-077F4CE50250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="120">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -390,6 +390,12 @@
   </si>
   <si>
     <t>def Zimbabwe by 84 runs</t>
+  </si>
+  <si>
+    <t>def Zimbabwe by 1 wicket</t>
+  </si>
+  <si>
+    <t>Durban</t>
   </si>
 </sst>
 </file>
@@ -1793,10 +1799,14 @@
         <v>90</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="10"/>
+        <v>63</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>118</v>
+      </c>
       <c r="I11" s="5"/>
       <c r="J11" s="6" t="str">
         <f>IF(B11="","",IFERROR(LOOKUP(2,1/($B$2:B10=B11),$L$2:L10),VLOOKUP(B11,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1804,7 +1814,7 @@
       </c>
       <c r="K11" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Scheduled</v>
+        <v>Defence</v>
       </c>
       <c r="L11" s="6" t="str">
         <f t="shared" si="1"/>
@@ -1816,7 +1826,7 @@
       </c>
       <c r="N11" s="6">
         <f>IF(B11="","",IF(K11="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B10=B11),$N$2:N10),VLOOKUP(B11,Baseline!$A$2:$H$10,6,FALSE))+IF(K11="Defence",1,0)))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O11" s="6">
         <f>IF(B11="","",IFERROR(LOOKUP(2,1/($B$2:B10=B11),$O$2:O10),VLOOKUP(B11,Baseline!$A$2:$H$10,7,FALSE))+IF(K11="Transfer",1,0))</f>
@@ -1824,7 +1834,7 @@
       </c>
       <c r="P11" s="6">
         <f>IF(B11="","",IFERROR(LOOKUP(2,1/($B$2:B10=B11),$P$2:P10),VLOOKUP(B11,Baseline!$A$2:$H$10,8,FALSE))+IF(K11="Defence",1,0))</f>
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="Q11" s="5"/>
       <c r="R11" s="12"/>
@@ -1832,43 +1842,53 @@
     <row r="12" spans="1:18">
       <c r="A12" s="6" t="str">
         <f>IF(OR(B12="",C12=""),"",VLOOKUP(B12,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C12,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B12,B12,$C$2:C12,C12),"00"))</f>
-        <v/>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+        <v>JEJ-20260924-01</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="7">
+        <v>46289</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="G12" s="5"/>
       <c r="H12" s="10"/>
       <c r="I12" s="5"/>
       <c r="J12" s="6" t="str">
         <f>IF(B12="","",IFERROR(LOOKUP(2,1/($B$2:B11=B12),$L$2:L11),VLOOKUP(B12,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v/>
+        <v>Australia</v>
       </c>
       <c r="K12" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="L12" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M12" s="8" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="M12" s="8">
         <f>IF(B12="","",IF(K12="Transfer",C12,IFERROR(LOOKUP(2,1/($B$2:B11=B12),$M$2:M11),VLOOKUP(B12,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v/>
-      </c>
-      <c r="N12" s="6" t="str">
+        <v>46187</v>
+      </c>
+      <c r="N12" s="6">
         <f>IF(B12="","",IF(K12="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B11=B12),$N$2:N11),VLOOKUP(B12,Baseline!$A$2:$H$10,6,FALSE))+IF(K12="Defence",1,0)))</f>
-        <v/>
-      </c>
-      <c r="O12" s="6" t="str">
+        <v>3</v>
+      </c>
+      <c r="O12" s="6">
         <f>IF(B12="","",IFERROR(LOOKUP(2,1/($B$2:B11=B12),$O$2:O11),VLOOKUP(B12,Baseline!$A$2:$H$10,7,FALSE))+IF(K12="Transfer",1,0))</f>
-        <v/>
-      </c>
-      <c r="P12" s="6" t="str">
+        <v>358</v>
+      </c>
+      <c r="P12" s="6">
         <f>IF(B12="","",IFERROR(LOOKUP(2,1/($B$2:B11=B12),$P$2:P11),VLOOKUP(B12,Baseline!$A$2:$H$10,8,FALSE))+IF(K12="Defence",1,0))</f>
-        <v/>
+        <v>599</v>
       </c>
       <c r="Q12" s="5"/>
       <c r="R12" s="12"/>
@@ -5888,7 +5908,7 @@
       </c>
       <c r="D4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$N$2:$N$100),VLOOKUP(A4,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$O$2:$O$100),VLOOKUP(A4,Baseline!$A$2:$H$10,7,FALSE))</f>
@@ -5896,15 +5916,15 @@
       </c>
       <c r="F4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$P$2:$P$100),VLOOKUP(A4,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G4" s="4">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A4)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
-        <v>46285</v>
+        <v>46289</v>
       </c>
       <c r="H4" t="str">
         <f>IF(G4="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A4)*(Updates!$C$2:$C$100=G4)),Updates!$D$2:$D$100),"TBD"))</f>
-        <v>Zimbabwe</v>
+        <v>South Africa</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6228,7 +6248,7 @@
       </c>
       <c r="D4">
         <f>Dashboard!D4</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <f>Dashboard!E4</f>
@@ -6236,15 +6256,15 @@
       </c>
       <c r="F4">
         <f>Dashboard!F4</f>
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G4" s="9">
         <f>Dashboard!G4</f>
-        <v>46285</v>
+        <v>46289</v>
       </c>
       <c r="H4" t="str">
         <f>Dashboard!H4</f>
-        <v>Zimbabwe</v>
+        <v>South Africa</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\lineal website\Live Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA03D3B-9C2B-411F-BD3B-077F4CE50250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32C48FA-1C55-41BD-B5E0-BB26DC1BA3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1770" yWindow="3210" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="START HERE" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="122">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -396,6 +396,12 @@
   </si>
   <si>
     <t>Durban</t>
+  </si>
+  <si>
+    <t>def Australia by 67 runs</t>
+  </si>
+  <si>
+    <t>Johannesburg</t>
   </si>
 </sst>
 </file>
@@ -1857,10 +1863,14 @@
         <v>119</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="10"/>
+        <v>63</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>120</v>
+      </c>
       <c r="I12" s="5"/>
       <c r="J12" s="6" t="str">
         <f>IF(B12="","",IFERROR(LOOKUP(2,1/($B$2:B11=B12),$L$2:L11),VLOOKUP(B12,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1868,23 +1878,23 @@
       </c>
       <c r="K12" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Scheduled</v>
+        <v>Transfer</v>
       </c>
       <c r="L12" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Australia</v>
+        <v>South Africa</v>
       </c>
       <c r="M12" s="8">
         <f>IF(B12="","",IF(K12="Transfer",C12,IFERROR(LOOKUP(2,1/($B$2:B11=B12),$M$2:M11),VLOOKUP(B12,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v>46187</v>
+        <v>46289</v>
       </c>
       <c r="N12" s="6">
         <f>IF(B12="","",IF(K12="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B11=B12),$N$2:N11),VLOOKUP(B12,Baseline!$A$2:$H$10,6,FALSE))+IF(K12="Defence",1,0)))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O12" s="6">
         <f>IF(B12="","",IFERROR(LOOKUP(2,1/($B$2:B11=B12),$O$2:O11),VLOOKUP(B12,Baseline!$A$2:$H$10,7,FALSE))+IF(K12="Transfer",1,0))</f>
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P12" s="6">
         <f>IF(B12="","",IFERROR(LOOKUP(2,1/($B$2:B11=B12),$P$2:P11),VLOOKUP(B12,Baseline!$A$2:$H$10,8,FALSE))+IF(K12="Defence",1,0))</f>
@@ -1896,43 +1906,53 @@
     <row r="13" spans="1:18">
       <c r="A13" s="6" t="str">
         <f>IF(OR(B13="",C13=""),"",VLOOKUP(B13,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C13,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B13,B13,$C$2:C13,C13),"00"))</f>
-        <v/>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+        <v>JEJ-20260927-01</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="7">
+        <v>46292</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="G13" s="5"/>
       <c r="H13" s="10"/>
       <c r="I13" s="5"/>
       <c r="J13" s="6" t="str">
         <f>IF(B13="","",IFERROR(LOOKUP(2,1/($B$2:B12=B13),$L$2:L12),VLOOKUP(B13,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v/>
+        <v>South Africa</v>
       </c>
       <c r="K13" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="L13" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M13" s="8" t="str">
+        <v>South Africa</v>
+      </c>
+      <c r="M13" s="8">
         <f>IF(B13="","",IF(K13="Transfer",C13,IFERROR(LOOKUP(2,1/($B$2:B12=B13),$M$2:M12),VLOOKUP(B13,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v/>
-      </c>
-      <c r="N13" s="6" t="str">
+        <v>46289</v>
+      </c>
+      <c r="N13" s="6">
         <f>IF(B13="","",IF(K13="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B12=B13),$N$2:N12),VLOOKUP(B13,Baseline!$A$2:$H$10,6,FALSE))+IF(K13="Defence",1,0)))</f>
-        <v/>
-      </c>
-      <c r="O13" s="6" t="str">
+        <v>0</v>
+      </c>
+      <c r="O13" s="6">
         <f>IF(B13="","",IFERROR(LOOKUP(2,1/($B$2:B12=B13),$O$2:O12),VLOOKUP(B13,Baseline!$A$2:$H$10,7,FALSE))+IF(K13="Transfer",1,0))</f>
-        <v/>
-      </c>
-      <c r="P13" s="6" t="str">
+        <v>359</v>
+      </c>
+      <c r="P13" s="6">
         <f>IF(B13="","",IFERROR(LOOKUP(2,1/($B$2:B12=B13),$P$2:P12),VLOOKUP(B13,Baseline!$A$2:$H$10,8,FALSE))+IF(K13="Defence",1,0))</f>
-        <v/>
+        <v>599</v>
       </c>
       <c r="Q13" s="5"/>
       <c r="R13" s="12"/>
@@ -5900,19 +5920,19 @@
       </c>
       <c r="B4" t="str">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$L$2:$L$100),VLOOKUP(A4,Baseline!$A$2:$H$10,4,FALSE))</f>
-        <v>Australia</v>
+        <v>South Africa</v>
       </c>
       <c r="C4" s="4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$M$2:$M$100),VLOOKUP(A4,Baseline!$A$2:$H$10,5,FALSE))</f>
-        <v>46187</v>
+        <v>46289</v>
       </c>
       <c r="D4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$N$2:$N$100),VLOOKUP(A4,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$O$2:$O$100),VLOOKUP(A4,Baseline!$A$2:$H$10,7,FALSE))</f>
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$P$2:$P$100),VLOOKUP(A4,Baseline!$A$2:$H$10,8,FALSE))</f>
@@ -5920,11 +5940,11 @@
       </c>
       <c r="G4" s="4">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A4)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="H4" t="str">
         <f>IF(G4="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A4)*(Updates!$C$2:$C$100=G4)),Updates!$D$2:$D$100),"TBD"))</f>
-        <v>South Africa</v>
+        <v>Australia</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6240,19 +6260,19 @@
       </c>
       <c r="B4" t="str">
         <f>Dashboard!B4</f>
-        <v>Australia</v>
+        <v>South Africa</v>
       </c>
       <c r="C4" s="9">
         <f>Dashboard!C4</f>
-        <v>46187</v>
+        <v>46289</v>
       </c>
       <c r="D4">
         <f>Dashboard!D4</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <f>Dashboard!E4</f>
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F4">
         <f>Dashboard!F4</f>
@@ -6260,11 +6280,11 @@
       </c>
       <c r="G4" s="9">
         <f>Dashboard!G4</f>
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="H4" t="str">
         <f>Dashboard!H4</f>
-        <v>South Africa</v>
+        <v>Australia</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\lineal website\Live Update\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\Lineal Sport Championship\Live Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32C48FA-1C55-41BD-B5E0-BB26DC1BA3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5500D5D-9A9C-430C-BD21-A03979B44E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="3210" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="START HERE" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="124">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -402,6 +402,12 @@
   </si>
   <si>
     <t>Johannesburg</t>
+  </si>
+  <si>
+    <t>def Australia by 32 runs</t>
+  </si>
+  <si>
+    <t>Potchefstroom</t>
   </si>
 </sst>
 </file>
@@ -1921,10 +1927,14 @@
         <v>121</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="10"/>
+        <v>63</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>122</v>
+      </c>
       <c r="I13" s="5"/>
       <c r="J13" s="6" t="str">
         <f>IF(B13="","",IFERROR(LOOKUP(2,1/($B$2:B12=B13),$L$2:L12),VLOOKUP(B13,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1932,7 +1942,7 @@
       </c>
       <c r="K13" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Scheduled</v>
+        <v>Defence</v>
       </c>
       <c r="L13" s="6" t="str">
         <f t="shared" si="1"/>
@@ -1944,7 +1954,7 @@
       </c>
       <c r="N13" s="6">
         <f>IF(B13="","",IF(K13="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B12=B13),$N$2:N12),VLOOKUP(B13,Baseline!$A$2:$H$10,6,FALSE))+IF(K13="Defence",1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="6">
         <f>IF(B13="","",IFERROR(LOOKUP(2,1/($B$2:B12=B13),$O$2:O12),VLOOKUP(B13,Baseline!$A$2:$H$10,7,FALSE))+IF(K13="Transfer",1,0))</f>
@@ -1952,7 +1962,7 @@
       </c>
       <c r="P13" s="6">
         <f>IF(B13="","",IFERROR(LOOKUP(2,1/($B$2:B12=B13),$P$2:P12),VLOOKUP(B13,Baseline!$A$2:$H$10,8,FALSE))+IF(K13="Defence",1,0))</f>
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="Q13" s="5"/>
       <c r="R13" s="12"/>
@@ -1960,43 +1970,53 @@
     <row r="14" spans="1:18">
       <c r="A14" s="6" t="str">
         <f>IF(OR(B14="",C14=""),"",VLOOKUP(B14,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C14,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B14,B14,$C$2:C14,C14),"00"))</f>
-        <v/>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+        <v>JEJ-20260930-01</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="7">
+        <v>46295</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="G14" s="5"/>
       <c r="H14" s="10"/>
       <c r="I14" s="5"/>
       <c r="J14" s="6" t="str">
         <f>IF(B14="","",IFERROR(LOOKUP(2,1/($B$2:B13=B14),$L$2:L13),VLOOKUP(B14,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v/>
+        <v>South Africa</v>
       </c>
       <c r="K14" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="L14" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M14" s="8" t="str">
+        <v>South Africa</v>
+      </c>
+      <c r="M14" s="8">
         <f>IF(B14="","",IF(K14="Transfer",C14,IFERROR(LOOKUP(2,1/($B$2:B13=B14),$M$2:M13),VLOOKUP(B14,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v/>
-      </c>
-      <c r="N14" s="6" t="str">
+        <v>46289</v>
+      </c>
+      <c r="N14" s="6">
         <f>IF(B14="","",IF(K14="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B13=B14),$N$2:N13),VLOOKUP(B14,Baseline!$A$2:$H$10,6,FALSE))+IF(K14="Defence",1,0)))</f>
-        <v/>
-      </c>
-      <c r="O14" s="6" t="str">
+        <v>1</v>
+      </c>
+      <c r="O14" s="6">
         <f>IF(B14="","",IFERROR(LOOKUP(2,1/($B$2:B13=B14),$O$2:O13),VLOOKUP(B14,Baseline!$A$2:$H$10,7,FALSE))+IF(K14="Transfer",1,0))</f>
-        <v/>
-      </c>
-      <c r="P14" s="6" t="str">
+        <v>359</v>
+      </c>
+      <c r="P14" s="6">
         <f>IF(B14="","",IFERROR(LOOKUP(2,1/($B$2:B13=B14),$P$2:P13),VLOOKUP(B14,Baseline!$A$2:$H$10,8,FALSE))+IF(K14="Defence",1,0))</f>
-        <v/>
+        <v>600</v>
       </c>
       <c r="Q14" s="5"/>
       <c r="R14" s="12"/>
@@ -5928,7 +5948,7 @@
       </c>
       <c r="D4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$N$2:$N$100),VLOOKUP(A4,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$O$2:$O$100),VLOOKUP(A4,Baseline!$A$2:$H$10,7,FALSE))</f>
@@ -5936,11 +5956,11 @@
       </c>
       <c r="F4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$P$2:$P$100),VLOOKUP(A4,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G4" s="4">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A4)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
-        <v>46292</v>
+        <v>46295</v>
       </c>
       <c r="H4" t="str">
         <f>IF(G4="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A4)*(Updates!$C$2:$C$100=G4)),Updates!$D$2:$D$100),"TBD"))</f>
@@ -6268,7 +6288,7 @@
       </c>
       <c r="D4">
         <f>Dashboard!D4</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <f>Dashboard!E4</f>
@@ -6276,11 +6296,11 @@
       </c>
       <c r="F4">
         <f>Dashboard!F4</f>
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G4" s="9">
         <f>Dashboard!G4</f>
-        <v>46292</v>
+        <v>46295</v>
       </c>
       <c r="H4" t="str">
         <f>Dashboard!H4</f>

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\Lineal Sport Championship\Live Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5500D5D-9A9C-430C-BD21-A03979B44E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F875258-D1E4-4F7E-BD40-F07ED8DB24D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="127">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -408,6 +408,15 @@
   </si>
   <si>
     <t>Potchefstroom</t>
+  </si>
+  <si>
+    <t>def South Africa by 45 runs (DLS)</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>Perth</t>
   </si>
 </sst>
 </file>
@@ -1985,10 +1994,14 @@
         <v>123</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="10"/>
+        <v>63</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>124</v>
+      </c>
       <c r="I14" s="5"/>
       <c r="J14" s="6" t="str">
         <f>IF(B14="","",IFERROR(LOOKUP(2,1/($B$2:B13=B14),$L$2:L13),VLOOKUP(B14,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1996,23 +2009,23 @@
       </c>
       <c r="K14" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Scheduled</v>
+        <v>Transfer</v>
       </c>
       <c r="L14" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>South Africa</v>
+        <v>Australia</v>
       </c>
       <c r="M14" s="8">
         <f>IF(B14="","",IF(K14="Transfer",C14,IFERROR(LOOKUP(2,1/($B$2:B13=B14),$M$2:M13),VLOOKUP(B14,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="N14" s="6">
         <f>IF(B14="","",IF(K14="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B13=B14),$N$2:N13),VLOOKUP(B14,Baseline!$A$2:$H$10,6,FALSE))+IF(K14="Defence",1,0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="6">
         <f>IF(B14="","",IFERROR(LOOKUP(2,1/($B$2:B13=B14),$O$2:O13),VLOOKUP(B14,Baseline!$A$2:$H$10,7,FALSE))+IF(K14="Transfer",1,0))</f>
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P14" s="6">
         <f>IF(B14="","",IFERROR(LOOKUP(2,1/($B$2:B13=B14),$P$2:P13),VLOOKUP(B14,Baseline!$A$2:$H$10,8,FALSE))+IF(K14="Defence",1,0))</f>
@@ -2024,43 +2037,53 @@
     <row r="15" spans="1:18">
       <c r="A15" s="6" t="str">
         <f>IF(OR(B15="",C15=""),"",VLOOKUP(B15,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C15,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B15,B15,$C$2:C15,C15),"00"))</f>
-        <v/>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+        <v>JEJ-20261113-01</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="7">
+        <v>46339</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="G15" s="5"/>
       <c r="H15" s="10"/>
       <c r="I15" s="5"/>
       <c r="J15" s="6" t="str">
         <f>IF(B15="","",IFERROR(LOOKUP(2,1/($B$2:B14=B15),$L$2:L14),VLOOKUP(B15,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v/>
+        <v>Australia</v>
       </c>
       <c r="K15" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="L15" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M15" s="8" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="M15" s="8">
         <f>IF(B15="","",IF(K15="Transfer",C15,IFERROR(LOOKUP(2,1/($B$2:B14=B15),$M$2:M14),VLOOKUP(B15,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v/>
-      </c>
-      <c r="N15" s="6" t="str">
+        <v>46295</v>
+      </c>
+      <c r="N15" s="6">
         <f>IF(B15="","",IF(K15="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B14=B15),$N$2:N14),VLOOKUP(B15,Baseline!$A$2:$H$10,6,FALSE))+IF(K15="Defence",1,0)))</f>
-        <v/>
-      </c>
-      <c r="O15" s="6" t="str">
+        <v>0</v>
+      </c>
+      <c r="O15" s="6">
         <f>IF(B15="","",IFERROR(LOOKUP(2,1/($B$2:B14=B15),$O$2:O14),VLOOKUP(B15,Baseline!$A$2:$H$10,7,FALSE))+IF(K15="Transfer",1,0))</f>
-        <v/>
-      </c>
-      <c r="P15" s="6" t="str">
+        <v>360</v>
+      </c>
+      <c r="P15" s="6">
         <f>IF(B15="","",IFERROR(LOOKUP(2,1/($B$2:B14=B15),$P$2:P14),VLOOKUP(B15,Baseline!$A$2:$H$10,8,FALSE))+IF(K15="Defence",1,0))</f>
-        <v/>
+        <v>600</v>
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="12"/>
@@ -5940,19 +5963,19 @@
       </c>
       <c r="B4" t="str">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$L$2:$L$100),VLOOKUP(A4,Baseline!$A$2:$H$10,4,FALSE))</f>
-        <v>South Africa</v>
+        <v>Australia</v>
       </c>
       <c r="C4" s="4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$M$2:$M$100),VLOOKUP(A4,Baseline!$A$2:$H$10,5,FALSE))</f>
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="D4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$N$2:$N$100),VLOOKUP(A4,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$O$2:$O$100),VLOOKUP(A4,Baseline!$A$2:$H$10,7,FALSE))</f>
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A4),Updates!$P$2:$P$100),VLOOKUP(A4,Baseline!$A$2:$H$10,8,FALSE))</f>
@@ -5960,11 +5983,11 @@
       </c>
       <c r="G4" s="4">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A4)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
-        <v>46295</v>
+        <v>46339</v>
       </c>
       <c r="H4" t="str">
         <f>IF(G4="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A4)*(Updates!$C$2:$C$100=G4)),Updates!$D$2:$D$100),"TBD"))</f>
-        <v>Australia</v>
+        <v>England</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6280,19 +6303,19 @@
       </c>
       <c r="B4" t="str">
         <f>Dashboard!B4</f>
-        <v>South Africa</v>
+        <v>Australia</v>
       </c>
       <c r="C4" s="9">
         <f>Dashboard!C4</f>
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="D4">
         <f>Dashboard!D4</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <f>Dashboard!E4</f>
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F4">
         <f>Dashboard!F4</f>
@@ -6300,11 +6323,11 @@
       </c>
       <c r="G4" s="9">
         <f>Dashboard!G4</f>
-        <v>46295</v>
+        <v>46339</v>
       </c>
       <c r="H4" t="str">
         <f>Dashboard!H4</f>
-        <v>Australia</v>
+        <v>England</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\Lineal Sport Championship\Live Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F875258-D1E4-4F7E-BD40-F07ED8DB24D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CE86D6-CC6C-4AD0-8AEA-1C9A88D3FBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="START HERE" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="129">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -417,6 +417,12 @@
   </si>
   <si>
     <t>Perth</t>
+  </si>
+  <si>
+    <t>def Bangladesh by 7 Wickets</t>
+  </si>
+  <si>
+    <t>Brisbane</t>
   </si>
 </sst>
 </file>
@@ -1494,10 +1500,14 @@
         <v>92</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="10"/>
+        <v>63</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>127</v>
+      </c>
       <c r="I5" s="5"/>
       <c r="J5" s="6" t="str">
         <f>IF(B5="","",IFERROR(LOOKUP(2,1/($B$2:B4=B5),$L$2:L4),VLOOKUP(B5,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -1505,7 +1515,7 @@
       </c>
       <c r="K5" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Scheduled</v>
+        <v>Defence</v>
       </c>
       <c r="L5" s="6" t="str">
         <f t="shared" si="1"/>
@@ -1517,7 +1527,7 @@
       </c>
       <c r="N5" s="6">
         <f>IF(B5="","",IF(K5="INVALID — CHECK RESULT TYPE","",IF(K5="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B4=B5),$N$2:N4),VLOOKUP(B5,Baseline!$A$2:$H$10,6,FALSE))+IF(K5="Defence",1,0))))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O5" s="6">
         <f>IF(B5="","",IF(K5="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B4=B5),$O$2:O4),VLOOKUP(B5,Baseline!$A$2:$H$10,7,FALSE))+IF(K5="Transfer",1,0)))</f>
@@ -1525,7 +1535,7 @@
       </c>
       <c r="P5" s="6">
         <f>IF(B5="","",IF(K5="INVALID — CHECK RESULT TYPE","",IFERROR(LOOKUP(2,1/($B$2:B4=B5),$P$2:P4),VLOOKUP(B5,Baseline!$A$2:$H$10,8,FALSE))+IF(K5="Defence",1,0)))</f>
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q5" s="5"/>
       <c r="R5" s="12"/>
@@ -2091,43 +2101,53 @@
     <row r="16" spans="1:18">
       <c r="A16" s="6" t="str">
         <f>IF(OR(B16="",C16=""),"",VLOOKUP(B16,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C16,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B16,B16,$C$2:C16,C16),"00"))</f>
-        <v/>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+        <v>TMT-20261011-01</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="7">
+        <v>46306</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="G16" s="5"/>
       <c r="H16" s="10"/>
       <c r="I16" s="5"/>
       <c r="J16" s="6" t="str">
         <f>IF(B16="","",IFERROR(LOOKUP(2,1/($B$2:B15=B16),$L$2:L15),VLOOKUP(B16,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v/>
+        <v>Australia</v>
       </c>
       <c r="K16" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="L16" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M16" s="8" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="M16" s="8">
         <f>IF(B16="","",IF(K16="Transfer",C16,IFERROR(LOOKUP(2,1/($B$2:B15=B16),$M$2:M15),VLOOKUP(B16,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v/>
-      </c>
-      <c r="N16" s="6" t="str">
+        <v>46077</v>
+      </c>
+      <c r="N16" s="6">
         <f>IF(B16="","",IF(K16="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B15=B16),$N$2:N15),VLOOKUP(B16,Baseline!$A$2:$H$10,6,FALSE))+IF(K16="Defence",1,0)))</f>
-        <v/>
-      </c>
-      <c r="O16" s="6" t="str">
+        <v>6</v>
+      </c>
+      <c r="O16" s="6">
         <f>IF(B16="","",IFERROR(LOOKUP(2,1/($B$2:B15=B16),$O$2:O15),VLOOKUP(B16,Baseline!$A$2:$H$10,7,FALSE))+IF(K16="Transfer",1,0))</f>
-        <v/>
-      </c>
-      <c r="P16" s="6" t="str">
+        <v>120</v>
+      </c>
+      <c r="P16" s="6">
         <f>IF(B16="","",IFERROR(LOOKUP(2,1/($B$2:B15=B16),$P$2:P15),VLOOKUP(B16,Baseline!$A$2:$H$10,8,FALSE))+IF(K16="Defence",1,0))</f>
-        <v/>
+        <v>252</v>
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="12"/>
@@ -6004,7 +6024,7 @@
       </c>
       <c r="D5">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$N$2:$N$100),VLOOKUP(A5,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$O$2:$O$100),VLOOKUP(A5,Baseline!$A$2:$H$10,7,FALSE))</f>
@@ -6012,11 +6032,11 @@
       </c>
       <c r="F5">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$P$2:$P$100),VLOOKUP(A5,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G5" s="4">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A5)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="H5" t="str">
         <f>IF(G5="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A5)*(Updates!$C$2:$C$100=G5)),Updates!$D$2:$D$100),"TBD"))</f>
@@ -6345,7 +6365,7 @@
       </c>
       <c r="D5">
         <f>Dashboard!D5</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <f>Dashboard!E5</f>
@@ -6353,11 +6373,11 @@
       </c>
       <c r="F5">
         <f>Dashboard!F5</f>
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G5" s="9">
         <f>Dashboard!G5</f>
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="H5" t="str">
         <f>Dashboard!H5</f>

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\Lineal Sport Championship\Live Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CE86D6-CC6C-4AD0-8AEA-1C9A88D3FBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D06B68-FCE6-44DB-8B23-D0ABE251BEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="START HERE" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="130">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -423,6 +423,9 @@
   </si>
   <si>
     <t>Brisbane</t>
+  </si>
+  <si>
+    <t>def Bangladesh by 9 wickets</t>
   </si>
 </sst>
 </file>
@@ -2116,10 +2119,14 @@
         <v>128</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="10"/>
+        <v>63</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>129</v>
+      </c>
       <c r="I16" s="5"/>
       <c r="J16" s="6" t="str">
         <f>IF(B16="","",IFERROR(LOOKUP(2,1/($B$2:B15=B16),$L$2:L15),VLOOKUP(B16,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2127,7 +2134,7 @@
       </c>
       <c r="K16" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Scheduled</v>
+        <v>Defence</v>
       </c>
       <c r="L16" s="6" t="str">
         <f t="shared" si="1"/>
@@ -2139,7 +2146,7 @@
       </c>
       <c r="N16" s="6">
         <f>IF(B16="","",IF(K16="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B15=B16),$N$2:N15),VLOOKUP(B16,Baseline!$A$2:$H$10,6,FALSE))+IF(K16="Defence",1,0)))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O16" s="6">
         <f>IF(B16="","",IFERROR(LOOKUP(2,1/($B$2:B15=B16),$O$2:O15),VLOOKUP(B16,Baseline!$A$2:$H$10,7,FALSE))+IF(K16="Transfer",1,0))</f>
@@ -2147,7 +2154,7 @@
       </c>
       <c r="P16" s="6">
         <f>IF(B16="","",IFERROR(LOOKUP(2,1/($B$2:B15=B16),$P$2:P15),VLOOKUP(B16,Baseline!$A$2:$H$10,8,FALSE))+IF(K16="Defence",1,0))</f>
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="12"/>
@@ -2155,43 +2162,53 @@
     <row r="17" spans="1:18">
       <c r="A17" s="6" t="str">
         <f>IF(OR(B17="",C17=""),"",VLOOKUP(B17,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C17,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B17,B17,$C$2:C17,C17),"00"))</f>
-        <v/>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+        <v>TMT-20261014-01</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="7">
+        <v>46309</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="G17" s="5"/>
       <c r="H17" s="10"/>
       <c r="I17" s="5"/>
       <c r="J17" s="6" t="str">
         <f>IF(B17="","",IFERROR(LOOKUP(2,1/($B$2:B16=B17),$L$2:L16),VLOOKUP(B17,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v/>
+        <v>Australia</v>
       </c>
       <c r="K17" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="L17" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M17" s="8" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="M17" s="8">
         <f>IF(B17="","",IF(K17="Transfer",C17,IFERROR(LOOKUP(2,1/($B$2:B16=B17),$M$2:M16),VLOOKUP(B17,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v/>
-      </c>
-      <c r="N17" s="6" t="str">
+        <v>46077</v>
+      </c>
+      <c r="N17" s="6">
         <f>IF(B17="","",IF(K17="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B16=B17),$N$2:N16),VLOOKUP(B17,Baseline!$A$2:$H$10,6,FALSE))+IF(K17="Defence",1,0)))</f>
-        <v/>
-      </c>
-      <c r="O17" s="6" t="str">
+        <v>7</v>
+      </c>
+      <c r="O17" s="6">
         <f>IF(B17="","",IFERROR(LOOKUP(2,1/($B$2:B16=B17),$O$2:O16),VLOOKUP(B17,Baseline!$A$2:$H$10,7,FALSE))+IF(K17="Transfer",1,0))</f>
-        <v/>
-      </c>
-      <c r="P17" s="6" t="str">
+        <v>120</v>
+      </c>
+      <c r="P17" s="6">
         <f>IF(B17="","",IFERROR(LOOKUP(2,1/($B$2:B16=B17),$P$2:P16),VLOOKUP(B17,Baseline!$A$2:$H$10,8,FALSE))+IF(K17="Defence",1,0))</f>
-        <v/>
+        <v>253</v>
       </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="12"/>
@@ -6024,7 +6041,7 @@
       </c>
       <c r="D5">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$N$2:$N$100),VLOOKUP(A5,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$O$2:$O$100),VLOOKUP(A5,Baseline!$A$2:$H$10,7,FALSE))</f>
@@ -6032,11 +6049,11 @@
       </c>
       <c r="F5">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$P$2:$P$100),VLOOKUP(A5,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G5" s="4">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A5)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="H5" t="str">
         <f>IF(G5="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A5)*(Updates!$C$2:$C$100=G5)),Updates!$D$2:$D$100),"TBD"))</f>
@@ -6365,7 +6382,7 @@
       </c>
       <c r="D5">
         <f>Dashboard!D5</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <f>Dashboard!E5</f>
@@ -6373,11 +6390,11 @@
       </c>
       <c r="F5">
         <f>Dashboard!F5</f>
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G5" s="9">
         <f>Dashboard!G5</f>
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="H5" t="str">
         <f>Dashboard!H5</f>

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\Lineal Sport Championship\Live Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D06B68-FCE6-44DB-8B23-D0ABE251BEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73291F46-89A1-401F-80BA-E18D68A63FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="132">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -426,6 +426,12 @@
   </si>
   <si>
     <t>def Bangladesh by 9 wickets</t>
+  </si>
+  <si>
+    <t>Australia win by 214 runs</t>
+  </si>
+  <si>
+    <t>Gqebhera</t>
   </si>
 </sst>
 </file>
@@ -1333,10 +1339,14 @@
         <v>88</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="10"/>
+        <v>63</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>130</v>
+      </c>
       <c r="I2" s="5"/>
       <c r="J2" s="6" t="str">
         <f>IF(B2="","",VLOOKUP(B2,Baseline!$A$2:$H$10,4,FALSE))</f>
@@ -1344,23 +1354,23 @@
       </c>
       <c r="K2" s="6" t="str">
         <f t="shared" ref="K2:K33" si="0">IF(B2="","",IF(F2&lt;&gt;"Completed",F2,IF(G2="Challenger win","Transfer",IF(OR(G2="Holder win",G2="Draw / tie"),"Defence",IF(G2="No result","No result","INVALID — CHECK RESULT TYPE")))))</f>
-        <v>Scheduled</v>
+        <v>Transfer</v>
       </c>
       <c r="L2" s="6" t="str">
         <f t="shared" ref="L2:L33" si="1">IF(B2="","",IF(K2="INVALID — CHECK RESULT TYPE","",IF(K2="Transfer",D2,J2)))</f>
-        <v>South Africa</v>
+        <v>Australia</v>
       </c>
       <c r="M2" s="8">
         <f>IF(B2="","",IF(K2="INVALID — CHECK RESULT TYPE","",IF(K2="Transfer",IF(R2&lt;&gt;"",R2,C2),VLOOKUP(B2,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v>45953</v>
+        <v>46308</v>
       </c>
       <c r="N2" s="6">
         <f>IF(B2="","",IF(K2="INVALID — CHECK RESULT TYPE","",IF(K2="Transfer",0,VLOOKUP(B2,Baseline!$A$2:$H$10,6,FALSE)+IF(K2="Defence",1,0))))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O2" s="6">
         <f>IF(B2="","",IF(K2="INVALID — CHECK RESULT TYPE","",VLOOKUP(B2,Baseline!$A$2:$H$10,7,FALSE)+IF(K2="Transfer",1,0)))</f>
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P2" s="6">
         <f>IF(B2="","",IF(K2="INVALID — CHECK RESULT TYPE","",VLOOKUP(B2,Baseline!$A$2:$H$10,8,FALSE)+IF(K2="Defence",1,0)))</f>
@@ -2216,43 +2226,53 @@
     <row r="18" spans="1:18">
       <c r="A18" s="6" t="str">
         <f>IF(OR(B18="",C18=""),"",VLOOKUP(B18,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C18,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B18,B18,$C$2:C18,C18),"00"))</f>
-        <v/>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+        <v>CBB-20261018-01</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="7">
+        <v>46313</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="G18" s="5"/>
       <c r="H18" s="10"/>
       <c r="I18" s="5"/>
       <c r="J18" s="6" t="str">
         <f>IF(B18="","",IFERROR(LOOKUP(2,1/($B$2:B17=B18),$L$2:L17),VLOOKUP(B18,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v/>
+        <v>Australia</v>
       </c>
       <c r="K18" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="L18" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M18" s="8" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="M18" s="8">
         <f>IF(B18="","",IF(K18="Transfer",C18,IFERROR(LOOKUP(2,1/($B$2:B17=B18),$M$2:M17),VLOOKUP(B18,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v/>
-      </c>
-      <c r="N18" s="6" t="str">
+        <v>46308</v>
+      </c>
+      <c r="N18" s="6">
         <f>IF(B18="","",IF(K18="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B17=B18),$N$2:N17),VLOOKUP(B18,Baseline!$A$2:$H$10,6,FALSE))+IF(K18="Defence",1,0)))</f>
-        <v/>
-      </c>
-      <c r="O18" s="6" t="str">
+        <v>0</v>
+      </c>
+      <c r="O18" s="6">
         <f>IF(B18="","",IFERROR(LOOKUP(2,1/($B$2:B17=B18),$O$2:O17),VLOOKUP(B18,Baseline!$A$2:$H$10,7,FALSE))+IF(K18="Transfer",1,0))</f>
-        <v/>
-      </c>
-      <c r="P18" s="6" t="str">
+        <v>215</v>
+      </c>
+      <c r="P18" s="6">
         <f>IF(B18="","",IFERROR(LOOKUP(2,1/($B$2:B17=B18),$P$2:P17),VLOOKUP(B18,Baseline!$A$2:$H$10,8,FALSE))+IF(K18="Defence",1,0))</f>
-        <v/>
+        <v>404</v>
       </c>
       <c r="Q18" s="5"/>
       <c r="R18" s="12"/>
@@ -5934,19 +5954,19 @@
       </c>
       <c r="B2" t="str">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$L$2:$L$100),VLOOKUP(A2,Baseline!$A$2:$H$10,4,FALSE))</f>
-        <v>South Africa</v>
+        <v>Australia</v>
       </c>
       <c r="C2" s="4">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$M$2:$M$100),VLOOKUP(A2,Baseline!$A$2:$H$10,5,FALSE))</f>
-        <v>45953</v>
+        <v>46308</v>
       </c>
       <c r="D2">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$N$2:$N$100),VLOOKUP(A2,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$O$2:$O$100),VLOOKUP(A2,Baseline!$A$2:$H$10,7,FALSE))</f>
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F2">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A2),Updates!$P$2:$P$100),VLOOKUP(A2,Baseline!$A$2:$H$10,8,FALSE))</f>
@@ -5954,11 +5974,11 @@
       </c>
       <c r="G2" s="4">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A2)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
-        <v>46304</v>
+        <v>46313</v>
       </c>
       <c r="H2" t="str">
         <f>IF(G2="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A2)*(Updates!$C$2:$C$100=G2)),Updates!$D$2:$D$100),"TBD"))</f>
-        <v>Australia</v>
+        <v>South Africa</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6272,19 +6292,19 @@
       </c>
       <c r="B2" t="str">
         <f>Dashboard!B2</f>
-        <v>South Africa</v>
+        <v>Australia</v>
       </c>
       <c r="C2" s="9">
         <f>Dashboard!C2</f>
-        <v>45953</v>
+        <v>46308</v>
       </c>
       <c r="D2">
         <f>Dashboard!D2</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <f>Dashboard!E2</f>
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F2">
         <f>Dashboard!F2</f>
@@ -6292,11 +6312,11 @@
       </c>
       <c r="G2" s="9">
         <f>Dashboard!G2</f>
-        <v>46304</v>
+        <v>46313</v>
       </c>
       <c r="H2" t="str">
         <f>Dashboard!H2</f>
-        <v>Australia</v>
+        <v>South Africa</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/LSC_Update_System.xlsx
+++ b/LSC_Update_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CH\Desktop\Lineal Sport Championship\Live Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73291F46-89A1-401F-80BA-E18D68A63FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B6CC7F-0C70-4512-A4D6-D99D964E341E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="135">
   <si>
     <t>LSC UPDATE SYSTEM — SAFE TEST</t>
   </si>
@@ -432,6 +432,15 @@
   </si>
   <si>
     <t>Gqebhera</t>
+  </si>
+  <si>
+    <t>def Bangladesh by 8 wickets</t>
+  </si>
+  <si>
+    <t>Sri Lanka</t>
+  </si>
+  <si>
+    <t>Dambulla</t>
   </si>
 </sst>
 </file>
@@ -2187,10 +2196,14 @@
         <v>128</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="10"/>
+        <v>63</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>132</v>
+      </c>
       <c r="I17" s="5"/>
       <c r="J17" s="6" t="str">
         <f>IF(B17="","",IFERROR(LOOKUP(2,1/($B$2:B16=B17),$L$2:L16),VLOOKUP(B17,Baseline!$A$2:$H$10,4,FALSE)))</f>
@@ -2198,7 +2211,7 @@
       </c>
       <c r="K17" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>Scheduled</v>
+        <v>Defence</v>
       </c>
       <c r="L17" s="6" t="str">
         <f t="shared" si="1"/>
@@ -2210,7 +2223,7 @@
       </c>
       <c r="N17" s="6">
         <f>IF(B17="","",IF(K17="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B16=B17),$N$2:N16),VLOOKUP(B17,Baseline!$A$2:$H$10,6,FALSE))+IF(K17="Defence",1,0)))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O17" s="6">
         <f>IF(B17="","",IFERROR(LOOKUP(2,1/($B$2:B16=B17),$O$2:O16),VLOOKUP(B17,Baseline!$A$2:$H$10,7,FALSE))+IF(K17="Transfer",1,0))</f>
@@ -2218,7 +2231,7 @@
       </c>
       <c r="P17" s="6">
         <f>IF(B17="","",IFERROR(LOOKUP(2,1/($B$2:B16=B17),$P$2:P16),VLOOKUP(B17,Baseline!$A$2:$H$10,8,FALSE))+IF(K17="Defence",1,0))</f>
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="12"/>
@@ -2280,43 +2293,53 @@
     <row r="19" spans="1:18">
       <c r="A19" s="6" t="str">
         <f>IF(OR(B19="",C19=""),"",VLOOKUP(B19,Lists!$A$2:$B$10,2,FALSE)&amp;"-"&amp;TEXT(C19,"yyyymmdd")&amp;"-"&amp;TEXT(COUNTIFS($B$2:B19,B19,$C$2:C19,C19),"00"))</f>
-        <v/>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+        <v>TMT-20261215-01</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="7">
+        <v>46371</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="G19" s="5"/>
       <c r="H19" s="10"/>
       <c r="I19" s="5"/>
       <c r="J19" s="6" t="str">
         <f>IF(B19="","",IFERROR(LOOKUP(2,1/($B$2:B18=B19),$L$2:L18),VLOOKUP(B19,Baseline!$A$2:$H$10,4,FALSE)))</f>
-        <v/>
+        <v>Australia</v>
       </c>
       <c r="K19" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="L19" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M19" s="8" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="M19" s="8">
         <f>IF(B19="","",IF(K19="Transfer",C19,IFERROR(LOOKUP(2,1/($B$2:B18=B19),$M$2:M18),VLOOKUP(B19,Baseline!$A$2:$H$10,5,FALSE))))</f>
-        <v/>
-      </c>
-      <c r="N19" s="6" t="str">
+        <v>46077</v>
+      </c>
+      <c r="N19" s="6">
         <f>IF(B19="","",IF(K19="Transfer",0,IFERROR(LOOKUP(2,1/($B$2:B18=B19),$N$2:N18),VLOOKUP(B19,Baseline!$A$2:$H$10,6,FALSE))+IF(K19="Defence",1,0)))</f>
-        <v/>
-      </c>
-      <c r="O19" s="6" t="str">
+        <v>8</v>
+      </c>
+      <c r="O19" s="6">
         <f>IF(B19="","",IFERROR(LOOKUP(2,1/($B$2:B18=B19),$O$2:O18),VLOOKUP(B19,Baseline!$A$2:$H$10,7,FALSE))+IF(K19="Transfer",1,0))</f>
-        <v/>
-      </c>
-      <c r="P19" s="6" t="str">
+        <v>120</v>
+      </c>
+      <c r="P19" s="6">
         <f>IF(B19="","",IFERROR(LOOKUP(2,1/($B$2:B18=B19),$P$2:P18),VLOOKUP(B19,Baseline!$A$2:$H$10,8,FALSE))+IF(K19="Defence",1,0))</f>
-        <v/>
+        <v>254</v>
       </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="12"/>
@@ -6061,7 +6084,7 @@
       </c>
       <c r="D5">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$N$2:$N$100),VLOOKUP(A5,Baseline!$A$2:$H$10,6,FALSE))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$O$2:$O$100),VLOOKUP(A5,Baseline!$A$2:$H$10,7,FALSE))</f>
@@ -6069,15 +6092,15 @@
       </c>
       <c r="F5">
         <f>IFERROR(LOOKUP(2,1/(Updates!$B$2:$B$100=A5),Updates!$P$2:$P$100),VLOOKUP(A5,Baseline!$A$2:$H$10,8,FALSE))</f>
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G5" s="4">
         <f>IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A5)*(Updates!$F$2:$F$100&lt;&gt;"Completed")*(Updates!$F$2:$F$100&lt;&gt;"Cancelled")*(Updates!$F$2:$F$100&lt;&gt;"Postponed")),Updates!$C$2:$C$100),"TBD")</f>
-        <v>46309</v>
+        <v>46371</v>
       </c>
       <c r="H5" t="str">
         <f>IF(G5="TBD","TBD",IFERROR(LOOKUP(2,1/((Updates!$B$2:$B$100=A5)*(Updates!$C$2:$C$100=G5)),Updates!$D$2:$D$100),"TBD"))</f>
-        <v>Bangladesh</v>
+        <v>Sri Lanka</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6402,7 +6425,7 @@
       </c>
       <c r="D5">
         <f>Dashboard!D5</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <f>Dashboard!E5</f>
@@ -6410,15 +6433,15 @@
       </c>
       <c r="F5">
         <f>Dashboard!F5</f>
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G5" s="9">
         <f>Dashboard!G5</f>
-        <v>46309</v>
+        <v>46371</v>
       </c>
       <c r="H5" t="str">
         <f>Dashboard!H5</f>
-        <v>Bangladesh</v>
+        <v>Sri Lanka</v>
       </c>
     </row>
     <row r="6" spans="1:8">
